--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1597-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1597-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DCBEA92-3367-4D9C-9873-FF650F929D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A047FB44-66A9-4111-AE24-DF96BCE95AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{D44E8272-5073-41E7-B5C1-69A256094C89}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{89A5A495-6F3F-4428-B798-658A0AFD486D}"/>
   </bookViews>
   <sheets>
     <sheet name="1597-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1514,19 +1514,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CBBC393-630F-4EF9-B777-00FC8BF20407}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF39508E-EFB8-41B3-8E0B-154AD0ACD616}">
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
-    <col min="3" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
+    <col min="3" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1554,7 +1554,7 @@
       <c r="Q1" s="33"/>
       <c r="R1" s="25"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1584,7 +1584,7 @@
       <c r="Q2" s="35"/>
       <c r="R2" s="36"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1680,7 +1680,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="40">
         <v>2025</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="42">
         <v>2024</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="40">
         <v>2023</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="42">
         <v>2022</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="44" t="s">
         <v>25</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="45"/>
       <c r="B17" s="22" t="s">
         <v>36</v>
@@ -2366,7 +2366,7 @@
       <c r="Q17" s="49"/>
       <c r="R17" s="49"/>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>2021</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="42">
         <v>2020</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2019</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="42">
         <v>2018</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2017</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="42">
         <v>2016</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2015</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="42">
         <v>2014</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2013</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="42">
         <v>2012</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2011</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="42" t="s">
         <v>43</v>
       </c>
